--- a/dados/enviadas/Mercedes.xlsx
+++ b/dados/enviadas/Mercedes.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,18 +451,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="53" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="59" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="59" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,35 +479,40 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>MODALIDADE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>VALOR_ESTIMADO</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>ORGAO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>DATA_DISPUTA</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>LINK_PORTAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>LINK_PNCP</t>
         </is>
@@ -520,40 +526,41 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>018/2026</t>
+          <t>102/2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2586288</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ENGENHEIRO CALDAS</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>BLL Compras</t>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1981118.35</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE CAMPO GRANDE</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://bllcompras.com/Process/ProcessView?param1=[gkz]wpX4yaHNo96WJP7RvIhSXuxUSANlBbWrwza/S9PG1WBMIS0PRSbKKf6HGAWYWMK1aMrfcT_F6vwHMcdtOH2aKOsearLctBrUsj6A5iySk_E=</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18080655000182/2026/71</t>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/03501509000106/2026/102</t>
         </is>
       </c>
     </row>
@@ -565,42 +572,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SP114/2026/2026</t>
+          <t>027/2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
+          <t>Veículos diversos</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Sigiloso</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EMPRESA BAIANA DE AGUAS E SANEAMENTO S/A - EMBASA</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Novo Banco do Brasil</t>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>417483.27</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BELEM DE SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://licitacoes-e2.bb.com.br/aop-inter-estatico/visualizar-processo-publico/1097583</t>
+          <t>Portal de Compras Públicas</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/13504675000110/2026/212</t>
+          <t>https://www.portaldecompraspublicas.com.br/processos/PE/Prefeitura-Municipal-de-Belem-de-Sao-Francisco-4988/PE-027-2026-2026-514041</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/10113728000183/2026/53</t>
         </is>
       </c>
     </row>
@@ -612,45 +622,502 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>48/2026</t>
+          <t>(9217) | 21-0/2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>527000</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE QUARTEL GERAL</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>399612.8</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE SAUDE DE ARUANA</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/12213549000143/2026/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>048/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>957000</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BOM JESUS DA LAPA</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>BNC Compras</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://bnccompras.com/Process/ProcessView?param1=[gkz]Wh2eCuasAKovrf8IxtUETOteWo6ofcSKPIc5MYcB0pS_IHJFaUoyPtO69S5g_PCVMeSGMZ/cm8v_qmeSMKYia3Gpde9JJ51eB3od2tTCf6s=</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/14105183000114/2026/138</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>27/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2162000</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BURITIS</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>AMM Licita</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://app2.ammlicita.org.br/pesquisa/109991</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18296699000144/2026/278</t>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://app2.ammlicita.org.br/pesquisa/113754</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18125146000129/2026/75</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>195/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>822264.05</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE VOLTA REDONDA</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>ComprasGov</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=45006805001952026</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/32512501000143/2026/348</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>20/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>53214168</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>CONSORCIO INTERMUNICIPAL DO VALE DO PARANAPANEMA</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/51501484000193/2026/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>55/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>336749.08</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE MATELANDIA</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/76206465000165/2026/153</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PE 25/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4142165.57</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE JAGUARIAIVA</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/76910900000138/2026/55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PCE 145/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Ônibus</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>3110732.88</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SAO BENTO DO SUL</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/86051398000100/2026/155</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026.09.18.01-PE/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Caminhão</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>611500</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE IRAUCUBA</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/07683188000169/2026/117</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>045/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Ônibus</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1300495.45</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SIMAO DIAS</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/13108089000156/2026/112</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>075/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Micro-ônibus</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>588865.03</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE CRUZEIRO DA FORTALEZA</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Licitanet</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>https://licitanet.com.br/sessao/202988</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18468041000172/2026/36</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/enviadas/Mercedes.xlsx
+++ b/dados/enviadas/Mercedes.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$R$-416] #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="[$R$-416] #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -69,21 +70,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -451,673 +453,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="59" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>CLIENTE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MODALIDADE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>VALOR_ESTIMADO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ORGAO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>DATA_DISPUTA</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>LINK_PORTAL</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>LINK_PNCP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>102/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>024/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Veículos diversos</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>1981118.35</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE CAMPO GRANDE</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/03501509000106/2026/102</t>
+      <c r="E2" s="5" t="n">
+        <v>2645703.84</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE CAPIM GROSSO</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>46315.39583333334</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Licitanet</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>https://licitanet.com.br/sessao/201096</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/13230982000150/2026/168</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>027/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>133/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Micro-ônibus</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>417483.27</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BELEM DE SAO FRANCISCO</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="n">
+        <v>534114</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SANTA RITA DE JACUTINGA</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>46309.39583333334</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Portal de Compras Públicas</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.portaldecompraspublicas.com.br/processos/PE/Prefeitura-Municipal-de-Belem-de-Sao-Francisco-4988/PE-027-2026-2026-514041</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/10113728000183/2026/53</t>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.portaldecompraspublicas.com.br/processos/MG/Prefeitura-Municipal-de-Santa-Rita-de-Jacutinga-3481/PE-133-2026-2026-514738</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18338269000148/2026/28</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>(9217) | 21-0/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>44/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Caminhão</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>399612.8</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>FUNDO MUNICIPAL DE SAUDE DE ARUANA</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/12213549000143/2026/5</t>
+      <c r="E4" s="5" t="n">
+        <v>839250</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BAEPENDI</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>46311.39583333334</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Licitar Digital</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>https://app2.licitardigital.com.br/pesquisa/114944</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18008862000126/2026/81</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>048/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>71/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Caminhões</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>957000</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BOM JESUS DA LAPA</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>BNC Compras</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>https://bnccompras.com/Process/ProcessView?param1=[gkz]Wh2eCuasAKovrf8IxtUETOteWo6ofcSKPIc5MYcB0pS_IHJFaUoyPtO69S5g_PCVMeSGMZ/cm8v_qmeSMKYia3Gpde9JJ51eB3od2tTCf6s=</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/14105183000114/2026/138</t>
+      <c r="E5" s="5" t="n">
+        <v>104980650.6</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE DESENV. DO VALE DO SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>46309.41666666666</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>ComprasGov</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=19500605000712026</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/00399857000126/2026/330</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>27/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>72/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Caminhões</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>2162000</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BURITIS</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>AMM Licita</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>https://app2.ammlicita.org.br/pesquisa/113754</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18125146000129/2026/75</t>
+      <c r="E6" s="5" t="n">
+        <v>88511841.98999999</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE DESENV. DO VALE DO SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ComprasGov</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=19500605000722026</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/00399857000126/2026/331</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>195/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>206/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Viaturas de salvamento</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>822264.05</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE VOLTA REDONDA</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="n">
+        <v>21465000</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>AGENCIA DE MODERNIZACAO DA GESTAO DE PROCESSOS</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>46314.375</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>ComprasGov</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=45006805001952026</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/32512501000143/2026/348</t>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=92599805002062026</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/07424905000138/2026/333</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Mercedes</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>20/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026.09.18.01-PE/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Caminhão</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>53214168</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>CONSORCIO INTERMUNICIPAL DO VALE DO PARANAPANEMA</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/51501484000193/2026/41</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>55/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>336749.08</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE MATELANDIA</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/76206465000165/2026/153</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>PE 25/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>4142165.57</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE JAGUARIAIVA</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/76910900000138/2026/55</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>PCE 145/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Ônibus</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3110732.88</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE SAO BENTO DO SUL</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/86051398000100/2026/155</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>2026.09.18.01-PE/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Caminhão</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>611500</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>MUNICIPIO DE IRAUCUBA</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G8" s="6" t="n">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>https://pncp.gov.br/app/editais/07683188000169/2026/117</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>045/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Ônibus</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1300495.45</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE SIMAO DIAS</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/13108089000156/2026/112</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>075/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Micro-ônibus</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>588865.03</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE CRUZEIRO DA FORTALEZA</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Licitanet</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>https://licitanet.com.br/sessao/202988</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18468041000172/2026/36</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>